--- a/data/seed/portfolio/L-2025-9997/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-9997/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,26 +560,26 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>2117000</v>
+        <v>930000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>3263000</v>
+        <v>10228000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7866 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №49/26 от 02.07.2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>2693000</v>
+        <v>2267000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shodlik Polimer MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>296550042</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000908609924001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8169 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7866 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -681,35 +681,40 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>3556000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
+          <t>Farg'ona Agro Servis AJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16307000288870344417</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по с/ф №8169 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -717,33 +722,28 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>13901000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>259284135</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>16307000288870344417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №218/26 от 06.07.2026</t>
+          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -760,31 +760,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>8393000</v>
+        <v>12507000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shodlik Polimer MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>296550042</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000908609924001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -801,31 +801,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>5339000</v>
+        <v>5416000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xiva Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>363681351</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000227135955001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2590 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №80 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -842,31 +842,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>3996000</v>
+        <v>4049000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Farg'ona Agro Servis AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6455 06.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -883,31 +883,31 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2398000</v>
+        <v>1177000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №218/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -923,32 +923,32 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5731000</v>
+        <v>5769000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6049</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №285/26</t>
         </is>
       </c>
     </row>
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>7907000</v>
+        <v>2343000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1042,26 +1042,26 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>2733000</v>
+        <v>1234000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1081,40 +1081,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>1796000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>1164000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Oydin Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>384837443</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000094788329001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №2/26, НДС 12%</t>
+          <t>Аренда помещения за юль, дог. №20/20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1122,40 +1122,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>6210000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>1581000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5181</t>
+          <t>Tovar uchun to'lov, hisob-faktura №953 09.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1163,40 +1163,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>9878000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>5048000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Samarqand Metall Servis AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>288874543</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000561894363001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №953 09.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №2993</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1205,39 +1205,39 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1164000</v>
+        <v>5853000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>278856228</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000931877789001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №85/23</t>
+          <t>Оплата за упаковочные материалы, с/ф №9092</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,33 +1245,33 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>2399000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>6665000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Tong Metall XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>268135192</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000713595561001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №44/26 от 13.07.2026</t>
+          <t>Оплата за товары согласно с/ф №8311</t>
         </is>
       </c>
     </row>
@@ -1286,40 +1286,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>8911000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>10516000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Toshkent Qog'oz XK</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>316175280</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000440103357001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №13/26 от 13.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №178/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1329,38 +1329,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>3709000</v>
+        <v>1386000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №235/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №44/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1368,40 +1368,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>2758000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>9113000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №242/26 от 14.07.2026</t>
+          <t>Оплата за упаковочые материалы, с/ф №3106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1410,39 +1410,39 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4885000</v>
+        <v>10757000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>302486990</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000902957178001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №23/26</t>
+          <t>Оплата за сырье по договору №264/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1450,40 +1450,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>5336000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>16318000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ishonch Qog'oz MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>313143690</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000699283821001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №88/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №8381</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1493,38 +1493,38 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>5131000</v>
+        <v>1551000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9967 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №242/26 от 14.07.2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Социальный налог а июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>НДФ за июнь 2026</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
@@ -1614,33 +1614,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>10481000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>3406000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3767</t>
+          <t>Оплата за товар по счет-фактуре №9967 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1655,33 +1655,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>80763000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>3326000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Zafar Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>214369056</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000928382134001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №236/26 от 15.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №88/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1698,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>26142000</v>
+        <v>31711000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9608 за поставленный твар</t>
+          <t>Оплата по с/ф №2327 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>1606000</v>
+        <v>2482000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>263115606</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078551990001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №278/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №5590 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1780,38 +1780,38 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>3774000</v>
+        <v>1469000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8144 20.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №9608 за поставленный твар</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1821,31 +1821,31 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>3676000</v>
+        <v>1592000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7343 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №278/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1862,26 +1862,26 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>2026000</v>
+        <v>1380000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oydin Plastik XK</t>
+          <t>Farg'ona Agro Servis AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>279755435</t>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000710781000001</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>5197000</v>
+        <v>1092000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №133/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7343 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1943,39 +1943,39 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1872000</v>
+        <v>3355000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за упаковочные материалы, с/ф №7060</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1984,22 +1984,22 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>4430000</v>
+        <v>9677000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №13/26 от 22.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №126/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>1818000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>10467000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>367293874</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000820751913001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №146/26 от 24.07.2026</t>
+          <t>Оплата за товары согласно с/ф №6703</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,38 +2067,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>2608000</v>
+        <v>931000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №178/26 от 27.07.2026</t>
+          <t>Оплата за продукцию по дог. №133/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>2292000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>1926000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Samarqand Metall Servis AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>288874543</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000561894363001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №151/26 от 27.07.2026</t>
+          <t>Оплата за транспортные услуги по договору №253/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>1819000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1953000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №280/26 от 27.07.2026</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>727000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>16851000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000772462131001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Предоплата за товар по договору №146/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2231,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>5933000</v>
+        <v>3919000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №116/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №280/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,38 +2272,38 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>5154000</v>
+        <v>2656000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xiva Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>363681351</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000227135955001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8711 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата по счет-фактуре №5597 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>2769000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>727000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000455024869001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5190 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>7454000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Shartnoma №128/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №7670</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2394,39 +2394,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>3376000</v>
+        <v>1907000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>302486990</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000902957178001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8157</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №171/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2435,22 +2435,22 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>6346000</v>
+        <v>5849000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №269/26</t>
+          <t>Предоплата за материалы по договору №116/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2476,34 +2476,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>300000</v>
+        <v>17412000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Mehnat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Предоплата за материалы по договору №276/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2511,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>15471000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №284/26 от 31.07.2026, НДС 12%</t>
+          <t>Оплата за товар по с/ф №5190 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2554,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>11207000</v>
+        <v>4464000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №4/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №43/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2593,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>2481000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>5158000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5612 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8511</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2636,38 +2641,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>1532000</v>
+        <v>6043000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8614 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №128/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2675,40 +2680,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>6595000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>5418000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №256/26</t>
+          <t>Оплата за продукцию по дог. №178/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2716,40 +2721,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>10051000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>1820000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №75/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2987</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2758,22 +2763,17 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>5574000</v>
+        <v>300000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>358483744</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2783,14 +2783,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2306</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2799,39 +2799,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>7125000</v>
+        <v>20943000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3963</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №281/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2840,34 +2840,39 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>5200000</v>
+        <v>5695000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
+          <t>Mehnat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>16307000288870344417</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за транспортные услуги по дог. №186/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2875,40 +2880,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>2508000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>21807000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6115 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №1253</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2918,38 +2923,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1583000</v>
+        <v>1283000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3506 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №85/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2957,40 +2962,35 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>1162000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>259284135</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>16307000288870344417</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №245/26 от 06.08.2026</t>
+          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2999,32 +2999,32 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>2721000</v>
+        <v>8755000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Farovon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>217611921</t>
+          <t>230761102</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000307091263001</t>
+          <t>20208000824982055001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №236/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №5414</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №7584</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3547</t>
         </is>
       </c>
     </row>
@@ -3077,31 +3077,31 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>5877000</v>
+        <v>1902000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3417 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №245/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3116,33 +3116,33 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>2785000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Oydin Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>384837443</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000094788329001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3688 за поставленный товар</t>
+          <t>Арендная плата за август 2026 г. по договору №20/20</t>
         </is>
       </c>
     </row>
@@ -3157,23 +3157,23 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>2185000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>2503000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buxoro Mebel MChJ</t>
+          <t>Farovon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>281631156</t>
+          <t>230761102</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000610785519001</t>
+          <t>20208000824982055001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №139/26 от 10.08.2026</t>
+          <t>Предоплата за материалы по дог. №293/26</t>
         </is>
       </c>
     </row>
@@ -3198,23 +3198,23 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>2175000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>3558000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Gulshan Non MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>242797217</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000773553901001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №162/26 от 10.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №2585</t>
         </is>
       </c>
     </row>
@@ -3239,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>1493000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>9171000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Xiva Poligraf MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>363681351</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000227135955001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №62/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9834</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3280,23 +3280,23 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>1409000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>5323000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №308 10.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №8605</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3323,38 +3323,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>1025000</v>
+        <v>8927000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shodlik Polimer MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>296550042</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000908609924001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №201/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3364,38 +3364,38 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>834000</v>
+        <v>70586000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Xiva Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>363681351</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000227135955001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1154</t>
+          <t>Оплата за продукцию по договору №76/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3403,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>806000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>2308000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5869 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3445,39 +3445,39 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1320000</v>
+        <v>2308000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>278856228</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000931877789001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №85/23</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮЛЬ 2026 Г.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3486,22 +3486,22 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>4057000</v>
+        <v>3442000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>217611921</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000307091263001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3511,14 +3511,14 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №111/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №12/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>39884000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2331000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Toshkent Qog'oz XK</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>316175280</t>
+          <t>344243288</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000440103357001</t>
+          <t>20208000238985306001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6808</t>
+          <t>Оплата по счет-фактуре №6007 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>3994000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>18108000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №14/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №285/26</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,38 +3610,38 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>2239000</v>
+        <v>3556000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>344243288</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000238985306001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №154/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №220/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,40 +3649,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>2374000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>2069000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №78/26 от 12.08.2026</t>
+          <t>Оплата за сырье по договору №209/26 от 20.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3690,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>28020000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №27/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>2561000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>3772000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №36/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №73/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3772,40 +3772,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>7608000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>1181000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish AJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>386585861</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000591513641001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6555</t>
+          <t>Shartnoma №4/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>7138000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>2231000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №123/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>5881000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>2922000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Tong Metall XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>268135192</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000713595561001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №250/26 от 17.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №41/26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>2483000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>4514000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №290/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9688</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>1688000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>6271000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №38/26 от 17.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №92/26</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,38 +3979,38 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>1394000</v>
+        <v>1322000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6366 17.08.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6530 25.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4018,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>2308000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>23592000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Agro Servis AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА ИЮЛЬ</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №294/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4060,39 +4060,39 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>2308000</v>
+        <v>3979000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>230761102</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000824982055001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Оплата за товары согласно счет-фактуре №4634</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4101,39 +4101,39 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>2470000</v>
+        <v>825000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000455024869001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8275</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>6061000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>5487000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №271/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2198 28.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4184,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>46491000</v>
+        <v>1513000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6007 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1649 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>1535000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>1541000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shodlik Polimer MChJ</t>
+          <t>Tong Metall XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>296550042</t>
+          <t>268135192</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000908609924001</t>
+          <t>20208000713595561001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №122/26 от 18.08.2026</t>
+          <t>Предоплата за материалы по дог. №18/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>3612000</v>
+        <v>42558000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Buxoro Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>281631156</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000610785519001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №9273 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Предоплата за товар по дог. №146/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4307,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>1229000</v>
+        <v>13271000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9151 от 19.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №10/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4348,38 +4348,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>870000</v>
+        <v>2394000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №220/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №2024 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4389,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>15532000</v>
+        <v>2268000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №73/26 от 24.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7407</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4428,35 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>2240000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>336359903</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №677 за поставленный товар</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4464,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>1576000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2652000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №190/26, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №264/26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4505,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>996000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>2889000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4446 от 24.08.2026, в тч. НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6377</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4552,39 +4547,39 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2206000</v>
+        <v>5001000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата за упаковочные материалы, с/ф №6707</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4592,40 +4587,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>1541000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>20637000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №125/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5133</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4635,38 +4630,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>1252000</v>
+        <v>2125000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lazzat Agro MChJ</t>
+          <t>Farg'ona Agro Servis AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>348952560</t>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000838244350001</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №294/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №174/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4675,39 +4670,39 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>825000</v>
+        <v>4430000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Tong Metall XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>268135192</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000772462131001</t>
+          <t>20208000713595561001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №240/26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4716,39 +4711,39 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2818000</v>
+        <v>9120000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>217611921</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000307091263001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2555</t>
+          <t>Предоплата за материалы по дог. №213/26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4756,40 +4751,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>17826000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>2477000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>302486990</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000902957178001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №294/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3915 04.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4798,22 +4793,17 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>5158000</v>
+        <v>17510000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>358483744</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,14 +4813,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9677</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4828,35 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>2341000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>259284135</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>16307000288870344417</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1649 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4879,40 +4864,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>777000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>4152000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2198 28.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №5931</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4921,39 +4906,39 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>3154000</v>
+        <v>1365000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Oydin Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>302486990</t>
+          <t>384837443</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000902957178001</t>
+          <t>20208000094788329001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2509</t>
+          <t>Арендная плата за сентябрь 2026 г. по дог. №20/20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4962,22 +4947,22 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>13003000</v>
+        <v>4817000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4987,14 +4972,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №3/26</t>
+          <t>Оплата за товары согласно счет-фактуре №5556</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5004,38 +4989,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>8738000</v>
+        <v>3789000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>263115606</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000078551990001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2024 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №116/6, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,23 +5028,23 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>844000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>47987000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5069,14 +5054,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7407</t>
+          <t>Оплата за товары согласно счет-фактуре №8263</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,35 +5069,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>2556000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Lazzat Non MChJ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за товар по счет-фактуре №6257 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5120,40 +5110,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>2510000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>1931000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Toshkent Qog'oz XK</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>316175280</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000440103357001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №084</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6919 10.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5161,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>9457000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>1406000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №295/26</t>
+          <t>Оплата за продукцию по дог. №162/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5202,40 +5192,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>3248000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>9868000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Buxoro Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>281631156</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000610785519001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №97/26 от 01.09.2026</t>
+          <t>Оплата за сырье по договору №92/26 от 11.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5245,38 +5235,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>6883000</v>
+        <v>45162000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за подукцию по дог. №118/26, НДС 12%</t>
+          <t>SHARTNOMA №184/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5286,38 +5276,38 @@
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>5336000</v>
+        <v>40481000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oydin Plastik XK</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>279755435</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000710781000001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2948 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №101/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5327,38 +5317,38 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>4060000</v>
+        <v>15093000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lazzat Agro MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>348952560</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000838244350001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №71/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4546</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5366,40 +5356,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>2349000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>2388000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6682 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5407,40 +5397,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>7698000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>2388000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №725</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5449,39 +5439,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>8668000</v>
+        <v>3444000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №8/26 от 03.09.2026, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №221/26</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5489,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>5846000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>8837000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Mehnat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>395256038</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000824435073001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6505</t>
+          <t>Оплата за сырье по договору №217/26 от 16.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5532,38 +5522,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>5203000</v>
+        <v>2243000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Farg'ona Agro Servis AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>355004249</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000860992433001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4065 ОТ 04.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №6473 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5573,38 +5563,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>4836000</v>
+        <v>1946000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3212 от 04.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №225/26 от 23.09.2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5613,39 +5603,39 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>5406000</v>
+        <v>853000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nihol Tur Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>302486990</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000902957178001</t>
+          <t>20208000455024869001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2333</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5654,34 +5644,39 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>5200000</v>
+        <v>2241000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9997)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>16307000288870344417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9997 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5691,38 +5686,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>16804000</v>
+        <v>13179000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №250/26 ОТ 07.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7716 28.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5732,38 +5727,38 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>6642000</v>
+        <v>12162000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5175 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1892 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5773,38 +5768,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>4685000</v>
+        <v>8683000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8877 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5814,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>2786000</v>
+        <v>4216000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>336359903</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000381004978001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №43/26 от 07.09.2026</t>
+          <t>Предоплата за товар по договору №101/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,38 +5850,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>2554000</v>
+        <v>2920000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf MChJ</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>255442432</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000872389853001</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №90/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №176/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5896,38 +5891,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1872000</v>
+        <v>2297000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Andijon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>335990383</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000100497896001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6852 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1448</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5930,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>3765000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>2077000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Xiva Yog'och MChJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>217611921</t>
+          <t>344243288</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000307091263001</t>
+          <t>20208000238985306001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №68/26</t>
+          <t>Оплата по счет-фактуре №1282 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5977,17 +5972,22 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>17510000</v>
+        <v>3227000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Qarshi Non XK</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5997,14 +5997,14 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за сырье по дог. №181/26 от 28.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6013,22 +6013,22 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>88950000</v>
+        <v>5253000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Tong Metall XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>268135192</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000713595561001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6038,14 +6038,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №35/26</t>
+          <t>Оплата за сырье по дог. №205/26 от 28.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6054,22 +6054,22 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>1461000</v>
+        <v>20844000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Zafar Logistik MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>358483744</t>
+          <t>367293874</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000509478832001</t>
+          <t>20208000820751913001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №7/26</t>
+          <t>Оплата за товары согласно счет-фактуре №9198</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6095,39 +6095,39 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1365000</v>
+        <v>25339000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>278856228</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000931877789001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №85/23</t>
+          <t>Оплата за упаковочные материалы, с/ф №667</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6137,38 +6137,38 @@
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>1826000</v>
+        <v>17004000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Zafar Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>259284135</t>
+          <t>214369056</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000754988689001</t>
+          <t>20208000928382134001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №5/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,40 +6176,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>17614000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>10063000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Buxoro Mebel MChJ</t>
+          <t>Qarshi Non XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>281631156</t>
+          <t>375543527</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000610785519001</t>
+          <t>20208000078100099001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №41/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №36/26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6217,40 +6217,40 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>2388000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>5033000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Non MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>328413547</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000498868975001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Tovar uchun to'lov, h/f №757 30.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6259,1078 +6259,53 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2388000</v>
+        <v>300000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>2984000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Nihol Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>302486990</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000902957178001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №29/26</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>538195000</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>535495000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>4106000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>358483744</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000509478832001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №86/26 от 14.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>4513000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Toshkent Qog'oz XK</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>316175280</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000440103357001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №26/26 от 15.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>2156000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>358483744</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000509478832001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №145/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>3472000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>358483744</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000509478832001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №8601</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>5088000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №252/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>13436000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №80/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>11907000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Lazzat Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>348952560</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000838244350001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №160/26 от 21.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>5232000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>1831000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №7627 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>1711000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №8694 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>1392000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Zafar Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>358483744</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000509478832001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №290/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>2272000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>11052000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №2664 от 25.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>5192000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №4220 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>2785000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №1057 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>853000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000772462131001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>2035000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Xiva Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>217611921</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000307091263001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Предплата за материалы по договору №206/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>2242000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Xiva Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>217611921</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000307091263001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №7741</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Xiva Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>217611921</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000307091263001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №153/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>5368000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Sarbon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>259284135</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000754988689001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5294 29.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>3181000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Nihol Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>302486990</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000902957178001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №1/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>18198000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Toshkent Qog'oz XK</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>316175280</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000440103357001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №169/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>25454000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Qarshi Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>255442432</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000872389853001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №150 ОТ 30.09.2026, В Т.Ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Oqsaroy Bank ATB</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>531860000</v>
-      </c>
-      <c r="D176" s="4" t="n">
-        <v>529160000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C152" s="4" t="n">
         <v>15200000</v>
       </c>
-      <c r="D177" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
